--- a/Data/National Accounts/PSA-12CNS_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-12CNS_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79911C09-A31E-4581-B93C-576B909CDFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29013C08-2117-4326-9B52-52E89F034299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CNS" sheetId="1" r:id="rId1"/>
@@ -624,9 +624,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -634,6 +631,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23614,7 +23614,7 @@
     </row>
     <row r="3" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:69" x14ac:dyDescent="0.2">
@@ -23624,7 +23624,7 @@
     </row>
     <row r="6" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:69" x14ac:dyDescent="0.2">
@@ -23826,10 +23826,10 @@
         <v>1433803.8154259156</v>
       </c>
       <c r="Z12" s="8">
-        <v>1626491.8251600764</v>
+        <v>1624737.8029237916</v>
       </c>
       <c r="AA12" s="8">
-        <v>1349760.5226168416</v>
+        <v>1360951.4902957582</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -23951,10 +23951,10 @@
         <v>1206185.4819713612</v>
       </c>
       <c r="Z13" s="8">
-        <v>1346219.2325211747</v>
+        <v>1342981.1576850237</v>
       </c>
       <c r="AA13" s="8">
-        <v>1486567.3422226342</v>
+        <v>1482109.5315188291</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -24076,10 +24076,10 @@
         <v>1006804.7053990464</v>
       </c>
       <c r="Z14" s="8">
-        <v>1101577.8734959415</v>
+        <v>1103116.0425989488</v>
       </c>
       <c r="AA14" s="8">
-        <v>1228083.8135988754</v>
+        <v>1227895.506951727</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -24272,10 +24272,10 @@
         <v>3646794.002796323</v>
       </c>
       <c r="Z16" s="11">
-        <v>4074288.9311771928</v>
+        <v>4070835.0032077641</v>
       </c>
       <c r="AA16" s="11">
-        <v>4064411.678438351</v>
+        <v>4070956.5287663145</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -24497,10 +24497,10 @@
         <v>1833308.9028312422</v>
       </c>
       <c r="Z19" s="8">
-        <v>2047092.5254759088</v>
+        <v>2045728.0789297444</v>
       </c>
       <c r="AA19" s="8">
-        <v>2064551.7851221794</v>
+        <v>2069067.9568018978</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -24598,7 +24598,7 @@
     </row>
     <row r="27" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:69" x14ac:dyDescent="0.2">
@@ -24608,7 +24608,7 @@
     </row>
     <row r="30" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:69" x14ac:dyDescent="0.2">
@@ -24810,10 +24810,10 @@
         <v>1193153.5174408746</v>
       </c>
       <c r="Z36" s="8">
-        <v>1338902.688055566</v>
+        <v>1337545.4169210598</v>
       </c>
       <c r="AA36" s="8">
-        <v>1099500.5139034337</v>
+        <v>1109430.1281093832</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -24935,10 +24935,10 @@
         <v>1010051.4520818172</v>
       </c>
       <c r="Z37" s="8">
-        <v>1110346.6988230075</v>
+        <v>1107773.6009731325</v>
       </c>
       <c r="AA37" s="8">
-        <v>1219083.6075478226</v>
+        <v>1215912.6294030496</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -25060,10 +25060,10 @@
         <v>845209.70530487224</v>
       </c>
       <c r="Z38" s="8">
-        <v>916487.0530865927</v>
+        <v>917736.28473293537</v>
       </c>
       <c r="AA38" s="8">
-        <v>1012020.2474498879</v>
+        <v>1011891.953522421</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -25256,10 +25256,10 @@
         <v>3048414.674827564</v>
       </c>
       <c r="Z40" s="11">
-        <v>3365736.4399651662</v>
+        <v>3363055.3026271281</v>
       </c>
       <c r="AA40" s="11">
-        <v>3330604.3689011442</v>
+        <v>3337234.7110348535</v>
       </c>
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
@@ -25481,10 +25481,10 @@
         <v>1507363.7486189185</v>
       </c>
       <c r="Z43" s="8">
-        <v>1661464.1171081318</v>
+        <v>1660531.6406684122</v>
       </c>
       <c r="AA43" s="8">
-        <v>1657514.1976606855</v>
+        <v>1662025.1161887494</v>
       </c>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -25722,7 +25722,7 @@
     </row>
     <row r="51" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:60" x14ac:dyDescent="0.2">
@@ -25735,7 +25735,7 @@
     </row>
     <row r="54" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:60" x14ac:dyDescent="0.2">
@@ -25851,7 +25851,7 @@
         <v>49</v>
       </c>
       <c r="Z58" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA58" s="19"/>
     </row>
@@ -25932,10 +25932,10 @@
         <v>13.573719082846651</v>
       </c>
       <c r="Y60" s="20">
-        <v>13.438938274614799</v>
+        <v>13.316604785373556</v>
       </c>
       <c r="Z60" s="20">
-        <v>-17.013998980044022</v>
+        <v>-16.235623505118028</v>
       </c>
       <c r="AA60" s="20"/>
       <c r="AB60" s="9"/>
@@ -26046,10 +26046,10 @@
         <v>13.928402565542058</v>
       </c>
       <c r="Y61" s="20">
-        <v>11.609636547850471</v>
+        <v>11.341180751909462</v>
       </c>
       <c r="Z61" s="20">
-        <v>10.425353189956894</v>
+        <v>10.359666852931056</v>
       </c>
       <c r="AA61" s="20"/>
       <c r="AB61" s="9"/>
@@ -26160,10 +26160,10 @@
         <v>10.123876059311314</v>
       </c>
       <c r="Y62" s="20">
-        <v>9.4132623326717493</v>
+        <v>9.5660396384152193</v>
       </c>
       <c r="Z62" s="20">
-        <v>11.484066914076422</v>
+        <v>11.311544709185512</v>
       </c>
       <c r="AA62" s="20"/>
       <c r="AB62" s="9"/>
@@ -26336,10 +26336,10 @@
         <v>12.714941953784646</v>
       </c>
       <c r="Y64" s="20">
-        <v>11.722486327801107</v>
+        <v>11.627774974026252</v>
       </c>
       <c r="Z64" s="20">
-        <v>-0.24242887300552241</v>
+        <v>2.985273499291452E-3</v>
       </c>
       <c r="AA64" s="20"/>
       <c r="AB64" s="9"/>
@@ -26541,10 +26541,10 @@
         <v>13.500246417107803</v>
       </c>
       <c r="Y67" s="20">
-        <v>11.661080263915878</v>
+        <v>11.586654915080373</v>
       </c>
       <c r="Z67" s="20">
-        <v>0.85288082629347173</v>
+        <v>1.1409081252071474</v>
       </c>
       <c r="AA67" s="20"/>
       <c r="AB67" s="9"/>
@@ -26756,7 +26756,7 @@
     </row>
     <row r="75" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:60" x14ac:dyDescent="0.2">
@@ -26766,7 +26766,7 @@
     </row>
     <row r="78" spans="1:60" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:60" x14ac:dyDescent="0.2">
@@ -26882,7 +26882,7 @@
         <v>49</v>
       </c>
       <c r="Z82" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA82" s="17"/>
     </row>
@@ -26963,10 +26963,10 @@
         <v>9.8078676385289612</v>
       </c>
       <c r="Y84" s="20">
-        <v>12.215458319839698</v>
+        <v>12.101703374255067</v>
       </c>
       <c r="Z84" s="20">
-        <v>-17.880476026215646</v>
+        <v>-17.054769574612493</v>
       </c>
       <c r="AA84" s="20"/>
       <c r="AB84" s="9"/>
@@ -27077,10 +27077,10 @@
         <v>10.559271414710977</v>
       </c>
       <c r="Y85" s="20">
-        <v>9.9297166034930058</v>
+        <v>9.6749674177389835</v>
       </c>
       <c r="Z85" s="20">
-        <v>9.7930591264943274</v>
+        <v>9.7618347589183827</v>
       </c>
       <c r="AA85" s="20"/>
       <c r="AB85" s="9"/>
@@ -27191,10 +27191,10 @@
         <v>6.6769444410066541</v>
       </c>
       <c r="Y86" s="20">
-        <v>8.4330962285874733</v>
+        <v>8.5808976130843604</v>
       </c>
       <c r="Z86" s="20">
-        <v>10.423845491494248</v>
+        <v>10.259556078997718</v>
       </c>
       <c r="AA86" s="20"/>
       <c r="AB86" s="9"/>
@@ -27367,10 +27367,10 @@
         <v>9.1653605644957707</v>
       </c>
       <c r="Y88" s="20">
-        <v>10.409402885962422</v>
+        <v>10.321451028225411</v>
       </c>
       <c r="Z88" s="20">
-        <v>-1.043815274626354</v>
+        <v>-0.76777184044830449</v>
       </c>
       <c r="AA88" s="20"/>
       <c r="AB88" s="9"/>
@@ -27572,10 +27572,10 @@
         <v>8.8203247636036366</v>
       </c>
       <c r="Y91" s="20">
-        <v>10.223170660061555</v>
+        <v>10.16130925198577</v>
       </c>
       <c r="Z91" s="20">
-        <v>-0.23773727080674689</v>
+        <v>8.9939600291870647E-2</v>
       </c>
       <c r="AA91" s="20"/>
       <c r="AB91" s="9"/>
@@ -27800,7 +27800,7 @@
     </row>
     <row r="98" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100" spans="1:69" x14ac:dyDescent="0.2">
@@ -27810,7 +27810,7 @@
     </row>
     <row r="101" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:69" x14ac:dyDescent="0.2">
@@ -28012,10 +28012,10 @@
         <v>120.16926526782554</v>
       </c>
       <c r="Z107" s="23">
-        <v>121.47946521208081</v>
+        <v>121.47159882344999</v>
       </c>
       <c r="AA107" s="23">
-        <v>122.76124526990331</v>
+        <v>122.67122154100872</v>
       </c>
       <c r="AB107" s="9"/>
       <c r="AC107" s="9"/>
@@ -28137,10 +28137,10 @@
         <v>119.41822166438077</v>
       </c>
       <c r="Z108" s="23">
-        <v>121.24314270022123</v>
+        <v>121.23245729138799</v>
       </c>
       <c r="AA108" s="23">
-        <v>121.94137736072533</v>
+        <v>121.89276562136446</v>
       </c>
       <c r="AB108" s="9"/>
       <c r="AC108" s="9"/>
@@ -28262,10 +28262,10 @@
         <v>119.11892386941841</v>
       </c>
       <c r="Z109" s="23">
-        <v>120.19568304712985</v>
+        <v>120.19967619782624</v>
       </c>
       <c r="AA109" s="23">
-        <v>121.34972760608589</v>
+        <v>121.34650371291049</v>
       </c>
       <c r="AB109" s="9"/>
       <c r="AC109" s="9"/>
@@ -28458,10 +28458,10 @@
         <v>119.62919719911815</v>
       </c>
       <c r="Z111" s="23">
-        <v>121.05193035314909</v>
+        <v>121.04573481226247</v>
       </c>
       <c r="AA111" s="23">
-        <v>122.0322568597155</v>
+        <v>121.98592191629037</v>
       </c>
       <c r="AB111" s="9"/>
       <c r="AC111" s="9"/>
@@ -28683,10 +28683,10 @@
         <v>121.62352348668077</v>
       </c>
       <c r="Z114" s="23">
-        <v>123.2101556932198</v>
+        <v>123.19717546040133</v>
       </c>
       <c r="AA114" s="23">
-        <v>124.55711016146722</v>
+        <v>124.49077553933441</v>
       </c>
       <c r="AB114" s="9"/>
       <c r="AC114" s="9"/>
@@ -28782,7 +28782,7 @@
     </row>
     <row r="122" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="1:69" x14ac:dyDescent="0.2">
@@ -28792,7 +28792,7 @@
     </row>
     <row r="125" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:69" x14ac:dyDescent="0.2">
@@ -28994,10 +28994,10 @@
         <v>39.316830463319015</v>
       </c>
       <c r="Z131" s="23">
-        <v>39.920875829739714</v>
+        <v>39.911659441945439</v>
       </c>
       <c r="AA131" s="23">
-        <v>33.209247227029266</v>
+        <v>33.430754680846192</v>
       </c>
       <c r="AB131" s="9"/>
       <c r="AC131" s="9"/>
@@ -29119,10 +29119,10 @@
         <v>33.07522939454411</v>
       </c>
       <c r="Z132" s="23">
-        <v>33.041820432018518</v>
+        <v>32.990311732771588</v>
       </c>
       <c r="AA132" s="23">
-        <v>36.575215795901137</v>
+        <v>36.406911276155924</v>
       </c>
       <c r="AB132" s="9"/>
       <c r="AC132" s="9"/>
@@ -29244,10 +29244,10 @@
         <v>27.607940142136883</v>
       </c>
       <c r="Z133" s="23">
-        <v>27.037303738241764</v>
+        <v>27.09802882528297</v>
       </c>
       <c r="AA133" s="23">
-        <v>30.215536977069608</v>
+        <v>30.162334042997884</v>
       </c>
       <c r="AB133" s="9"/>
       <c r="AC133" s="9"/>
@@ -29852,7 +29852,7 @@
     </row>
     <row r="146" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="148" spans="1:69" x14ac:dyDescent="0.2">
@@ -29862,7 +29862,7 @@
     </row>
     <row r="149" spans="1:69" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="150" spans="1:69" x14ac:dyDescent="0.2">
@@ -30064,10 +30064,10 @@
         <v>39.14013166559652</v>
       </c>
       <c r="Z155" s="23">
-        <v>39.780378289793333</v>
+        <v>39.771734228580939</v>
       </c>
       <c r="AA155" s="23">
-        <v>33.012042023657962</v>
+        <v>33.243994629474429</v>
       </c>
       <c r="AB155" s="9"/>
       <c r="AC155" s="9"/>
@@ -30189,10 +30189,10 @@
         <v>33.133663225753615</v>
       </c>
       <c r="Z156" s="23">
-        <v>32.989710235139484</v>
+        <v>32.939499987043618</v>
       </c>
       <c r="AA156" s="23">
-        <v>36.602474281568028</v>
+        <v>36.434735183070281</v>
       </c>
       <c r="AB156" s="9"/>
       <c r="AC156" s="9"/>
@@ -30314,10 +30314,10 @@
         <v>27.726205108649864</v>
       </c>
       <c r="Z157" s="23">
-        <v>27.22991147506719</v>
+        <v>27.288765784375428</v>
       </c>
       <c r="AA157" s="23">
-        <v>30.385483694774006</v>
+        <v>30.321270187455298</v>
       </c>
       <c r="AB157" s="9"/>
       <c r="AC157" s="9"/>
